--- a/Final Project - Josie/Categorical_Regression_Analysis_SEX.xlsx
+++ b/Final Project - Josie/Categorical_Regression_Analysis_SEX.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ICEDTEATYPE</t>
+          <t>MILKTYPE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,40 +467,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>-46201836.31374656</v>
+        <v>0.5181584134390046</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01027068550065297</v>
+        <v>0.01087790765331289</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FATONMEATTYPE</t>
+          <t>MILKTYPE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>52134013.65437788</v>
+        <v>0.4482527416514952</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007949835661054722</v>
+        <v>0.01797142148923626</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SUGARINTEA</t>
+          <t>ICEDTEATYPE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -512,31 +512,94 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>-47656886.14202257</v>
+        <v>-0.3096223352909185</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004215761975341941</v>
+        <v>0.0007576999998037476</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>FATONMEATTYPE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1850048653706161</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0389061913435653</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CHICKENSKINTYPE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.2616078026036964</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.002964636861640332</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SUGARINTEA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2992378988697538</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0003921600498028904</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>SUGARINCOFFEE</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C8" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="n">
-        <v>-44206676.95419528</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.01426825008394087</v>
+      <c r="D8" t="n">
+        <v>-0.314819828836556</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0005571469465300123</v>
       </c>
     </row>
   </sheetData>
